--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>88.67327006458737</v>
+        <v>14.40940638549545</v>
       </c>
       <c r="D2" t="n">
-        <v>88.41267933786318</v>
+        <v>14.36706039240277</v>
       </c>
       <c r="E2" t="n">
-        <v>17.35654061004631</v>
+        <v>2.820437849132526</v>
       </c>
       <c r="F2" t="n">
-        <v>16.8433101248087</v>
+        <v>2.737037895281414</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.08906670022789</v>
+        <v>10.90197333878703</v>
       </c>
       <c r="D3" t="n">
-        <v>66.87893050382407</v>
+        <v>10.86782620687141</v>
       </c>
       <c r="E3" t="n">
-        <v>17.35654061004631</v>
+        <v>2.820437849132526</v>
       </c>
       <c r="F3" t="n">
-        <v>16.8433101248087</v>
+        <v>2.737037895281414</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.27913835057799</v>
+        <v>11.58285998196892</v>
       </c>
       <c r="D4" t="n">
-        <v>71.00978671606221</v>
+        <v>11.53909034136011</v>
       </c>
       <c r="E4" t="n">
-        <v>17.35654061004631</v>
+        <v>2.820437849132526</v>
       </c>
       <c r="F4" t="n">
-        <v>16.8433101248087</v>
+        <v>2.737037895281414</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>85.15493259919333</v>
+        <v>13.83767654736892</v>
       </c>
       <c r="D5" t="n">
-        <v>84.85980237663915</v>
+        <v>13.78971788620386</v>
       </c>
       <c r="E5" t="n">
-        <v>17.35654061004631</v>
+        <v>2.820437849132526</v>
       </c>
       <c r="F5" t="n">
-        <v>16.8433101248087</v>
+        <v>2.737037895281414</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>84.32398364954722</v>
+        <v>13.70264734305142</v>
       </c>
       <c r="D6" t="n">
-        <v>84.0301235713342</v>
+        <v>13.65489508034181</v>
       </c>
       <c r="E6" t="n">
-        <v>17.35654061004631</v>
+        <v>2.820437849132526</v>
       </c>
       <c r="F6" t="n">
-        <v>16.8433101248087</v>
+        <v>2.737037895281414</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.47865878039131</v>
+        <v>7.552782051813588</v>
       </c>
       <c r="D7" t="n">
-        <v>47.54801826004341</v>
+        <v>7.726552967257055</v>
       </c>
       <c r="E7" t="n">
-        <v>17.35654061004631</v>
+        <v>2.820437849132526</v>
       </c>
       <c r="F7" t="n">
-        <v>16.8433101248087</v>
+        <v>2.737037895281414</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.80542289143186</v>
+        <v>6.143381219857678</v>
       </c>
       <c r="D8" t="n">
-        <v>38.70420432070353</v>
+        <v>6.289433202114324</v>
       </c>
       <c r="E8" t="n">
-        <v>17.35654061004631</v>
+        <v>2.820437849132526</v>
       </c>
       <c r="F8" t="n">
-        <v>16.8433101248087</v>
+        <v>2.737037895281414</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>62.03742906657419</v>
+        <v>10.08108222331831</v>
       </c>
       <c r="D9" t="n">
-        <v>63.01353899959688</v>
+        <v>10.23970008743449</v>
       </c>
       <c r="E9" t="n">
-        <v>17.35654061004631</v>
+        <v>2.820437849132526</v>
       </c>
       <c r="F9" t="n">
-        <v>16.8433101248087</v>
+        <v>2.737037895281414</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
